--- a/data/trans_dic/MCS12_SP_R3-Edad-trans_dic.xlsx
+++ b/data/trans_dic/MCS12_SP_R3-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población en el primer cuartil (48.388) de la puntuación del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,14; 14,81</t>
+          <t>8,86; 14,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,81; 19,73</t>
+          <t>12,51; 19,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,29; 14,46</t>
+          <t>8,39; 14,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 13,38</t>
+          <t>4,07; 12,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,14; 22,34</t>
+          <t>15,35; 21,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,46; 22,07</t>
+          <t>14,64; 22,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,61; 16,59</t>
+          <t>9,81; 16,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,33; 27,91</t>
+          <t>14,92; 27,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,74; 17,6</t>
+          <t>12,88; 17,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,64; 19,95</t>
+          <t>14,37; 19,45</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,64; 14,35</t>
+          <t>9,7; 14,4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,96; 17,73</t>
+          <t>10,15; 18,06</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,72; 15,87</t>
+          <t>10,86; 16,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,46; 21,53</t>
+          <t>15,11; 21,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,61; 18,45</t>
+          <t>12,62; 18,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,82; 16,26</t>
+          <t>8,21; 16,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,6; 25,43</t>
+          <t>18,47; 25,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,96; 26,84</t>
+          <t>20,16; 27,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,82; 20,94</t>
+          <t>14,6; 20,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,09; 22,13</t>
+          <t>10,74; 22,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,1; 19,31</t>
+          <t>15,0; 19,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,11; 22,8</t>
+          <t>18,14; 22,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14,63; 18,84</t>
+          <t>14,52; 18,71</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,23; 17,99</t>
+          <t>11,42; 18,05</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,73; 24,47</t>
+          <t>17,88; 24,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,71; 26,23</t>
+          <t>19,9; 26,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,77; 20,71</t>
+          <t>15,05; 21,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,69; 21,46</t>
+          <t>15,02; 21,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,59; 28,27</t>
+          <t>21,75; 28,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,52; 37,17</t>
+          <t>29,64; 36,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,37; 25,86</t>
+          <t>19,52; 25,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,35; 22,87</t>
+          <t>17,18; 22,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,73; 25,53</t>
+          <t>20,94; 25,58</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25,69; 30,66</t>
+          <t>25,83; 30,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,76; 22,1</t>
+          <t>17,87; 22,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,81; 21,23</t>
+          <t>16,71; 21,21</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,66; 20,39</t>
+          <t>13,75; 20,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,99; 26,27</t>
+          <t>18,89; 26,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,92; 26,71</t>
+          <t>19,67; 26,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,43; 23,9</t>
+          <t>6,77; 23,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,33; 34,49</t>
+          <t>26,84; 35,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,28; 39,72</t>
+          <t>31,42; 39,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,54; 34,09</t>
+          <t>26,89; 34,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,68; 28,82</t>
+          <t>21,6; 28,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,48; 26,81</t>
+          <t>21,07; 26,83</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,22; 31,84</t>
+          <t>26,01; 31,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23,91; 29,04</t>
+          <t>24,2; 29,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,36; 24,66</t>
+          <t>11,72; 25,01</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,17; 29,77</t>
+          <t>21,06; 30,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,53; 31,27</t>
+          <t>22,88; 32,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,13; 25,53</t>
+          <t>17,87; 25,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20,88; 27,78</t>
+          <t>20,83; 27,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,14; 37,48</t>
+          <t>28,35; 37,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,96; 44,95</t>
+          <t>35,25; 44,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,35; 38,12</t>
+          <t>29,49; 38,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,38; 34,17</t>
+          <t>28,4; 34,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26,0; 32,14</t>
+          <t>26,03; 32,18</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,07; 36,92</t>
+          <t>30,24; 36,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24,73; 30,59</t>
+          <t>24,94; 30,63</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,29; 29,7</t>
+          <t>25,38; 29,99</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,59; 32,58</t>
+          <t>22,27; 32,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,95; 30,12</t>
+          <t>20,55; 30,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,14; 22,92</t>
+          <t>14,13; 22,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,38; 28,51</t>
+          <t>21,51; 28,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,03; 35,39</t>
+          <t>26,16; 35,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,87; 41,78</t>
+          <t>31,6; 41,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,06; 40,16</t>
+          <t>30,38; 40,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29,79; 80,61</t>
+          <t>29,93; 81,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25,56; 32,4</t>
+          <t>25,77; 32,49</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>27,72; 35,27</t>
+          <t>27,83; 34,94</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23,62; 30,7</t>
+          <t>23,9; 30,58</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>27,38; 68,78</t>
+          <t>27,38; 69,66</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,31; 33,11</t>
+          <t>20,94; 33,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25,66; 38,37</t>
+          <t>25,94; 39,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,35; 34,18</t>
+          <t>23,41; 33,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27,51; 36,19</t>
+          <t>27,34; 36,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,44; 37,08</t>
+          <t>26,62; 37,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,05; 51,48</t>
+          <t>40,97; 51,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,59; 45,03</t>
+          <t>33,7; 44,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>40,16; 46,99</t>
+          <t>39,47; 46,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>26,32; 34,09</t>
+          <t>26,1; 34,27</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36,78; 44,8</t>
+          <t>36,99; 44,85</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30,78; 38,59</t>
+          <t>30,82; 38,56</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36,01; 41,41</t>
+          <t>36,13; 41,36</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,32; 20,03</t>
+          <t>17,4; 20,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,83; 23,76</t>
+          <t>20,79; 23,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,49; 20,2</t>
+          <t>17,6; 20,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,1; 20,31</t>
+          <t>14,57; 20,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,9; 28,14</t>
+          <t>25,04; 28,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,08; 34,52</t>
+          <t>30,98; 34,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,34; 28,3</t>
+          <t>25,33; 28,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>26,16; 43,29</t>
+          <t>26,19; 43,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21,7; 23,73</t>
+          <t>21,74; 23,58</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26,45; 28,57</t>
+          <t>26,49; 28,69</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21,91; 23,92</t>
+          <t>21,93; 23,97</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,89; 32,04</t>
+          <t>21,81; 32,8</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población en el primer cuartil (48.388) de la puntuación del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>45180; 73180</t>
+          <t>43772; 73744</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>58191; 89617</t>
+          <t>56832; 87842</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34792; 60662</t>
+          <t>35175; 60985</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15349; 53520</t>
+          <t>16271; 51970</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>70760; 104436</t>
+          <t>71744; 102512</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62231; 94961</t>
+          <t>62973; 96611</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38016; 65638</t>
+          <t>38823; 65513</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47761; 86982</t>
+          <t>46484; 87081</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>122542; 169254</t>
+          <t>123868; 167754</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>129440; 176398</t>
+          <t>127093; 172033</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>78560; 117014</t>
+          <t>79059; 117356</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>70906; 126140</t>
+          <t>72263; 128490</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>78814; 116724</t>
+          <t>79909; 118084</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>106212; 147930</t>
+          <t>103811; 148205</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74478; 108974</t>
+          <t>74525; 110962</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33127; 68872</t>
+          <t>34765; 68161</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>116370; 159083</t>
+          <t>115526; 157718</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>121799; 163798</t>
+          <t>123040; 166086</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83494; 118015</t>
+          <t>82288; 117507</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>56662; 113074</t>
+          <t>54876; 114070</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>205541; 262850</t>
+          <t>204093; 263257</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>234988; 295749</t>
+          <t>235274; 294025</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>168828; 217426</t>
+          <t>167606; 215969</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>104978; 168101</t>
+          <t>106711; 168635</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>113234; 156312</t>
+          <t>114191; 156376</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>134429; 178879</t>
+          <t>135696; 181233</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>98847; 138587</t>
+          <t>100704; 140866</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>78649; 114903</t>
+          <t>80424; 115933</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>148887; 194989</t>
+          <t>150003; 196346</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>209810; 264251</t>
+          <t>210703; 262556</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>128107; 171020</t>
+          <t>129088; 170436</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>93989; 123873</t>
+          <t>93090; 123484</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>275411; 339170</t>
+          <t>278186; 339823</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>357730; 426961</t>
+          <t>359763; 429394</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>236327; 294018</t>
+          <t>237824; 297314</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>181051; 228638</t>
+          <t>179987; 228427</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>70900; 105859</t>
+          <t>71384; 105818</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>116701; 161460</t>
+          <t>116124; 160931</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>128671; 172543</t>
+          <t>127071; 170016</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56915; 211660</t>
+          <t>59944; 208628</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>135782; 177836</t>
+          <t>138414; 182276</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>192776; 244784</t>
+          <t>193611; 242169</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>172278; 221278</t>
+          <t>174544; 220896</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>153787; 204389</t>
+          <t>153242; 201844</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>222252; 277426</t>
+          <t>218024; 277671</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>322778; 391837</t>
+          <t>320159; 388127</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>309603; 376111</t>
+          <t>313393; 380013</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>181141; 393299</t>
+          <t>186933; 398924</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>81863; 115105</t>
+          <t>81433; 117149</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>96735; 134298</t>
+          <t>98265; 138623</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>86670; 122034</t>
+          <t>85409; 122719</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>115894; 154167</t>
+          <t>115569; 152569</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>113695; 151428</t>
+          <t>114529; 150945</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>156537; 201307</t>
+          <t>157828; 200240</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>145845; 189387</t>
+          <t>146508; 189039</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>154858; 186434</t>
+          <t>154962; 186218</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>205543; 254099</t>
+          <t>205846; 254480</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>263756; 323890</t>
+          <t>265256; 323335</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>241091; 298149</t>
+          <t>243152; 298576</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>278372; 326831</t>
+          <t>279307; 330089</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>66086; 95333</t>
+          <t>65144; 94139</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>61793; 93323</t>
+          <t>63651; 95960</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47282; 76622</t>
+          <t>47227; 76409</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>77763; 103726</t>
+          <t>78243; 103575</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>89279; 121364</t>
+          <t>89703; 121513</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>112833; 147889</t>
+          <t>111873; 148487</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>113568; 151696</t>
+          <t>114773; 152679</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>180746; 489042</t>
+          <t>181560; 492062</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>162429; 205923</t>
+          <t>163787; 206472</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>184029; 234097</t>
+          <t>184740; 231900</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>168196; 218578</t>
+          <t>170186; 217766</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>265674; 667429</t>
+          <t>265733; 676017</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>44735; 69486</t>
+          <t>43955; 69593</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>64109; 95874</t>
+          <t>64803; 97493</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>60003; 87831</t>
+          <t>60166; 87318</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>77148; 101475</t>
+          <t>76669; 101077</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>88271; 123806</t>
+          <t>88872; 124721</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>159667; 200257</t>
+          <t>159358; 199078</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>134420; 180205</t>
+          <t>134849; 179758</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>167748; 196282</t>
+          <t>164866; 195109</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>143137; 185401</t>
+          <t>141912; 186334</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>234937; 286175</t>
+          <t>236321; 286526</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>202289; 253618</t>
+          <t>202518; 253390</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>251362; 289108</t>
+          <t>252206; 288745</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>567515; 656212</t>
+          <t>570263; 662516</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>713821; 814262</t>
+          <t>712305; 815399</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>593816; 685543</t>
+          <t>597445; 688115</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>485466; 699541</t>
+          <t>501790; 702537</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>841377; 950929</t>
+          <t>846053; 947894</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1105945; 1228193</t>
+          <t>1102324; 1216963</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>898089; 1003188</t>
+          <t>897801; 1007196</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>953102; 1577346</t>
+          <t>954129; 1594929</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1444252; 1579259</t>
+          <t>1446647; 1569483</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1847857; 1995433</t>
+          <t>1850649; 2004043</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1519999; 1660006</t>
+          <t>1521629; 1663316</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1551484; 2271052</t>
+          <t>1545530; 2324808</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/MCS12_SP_R3-Edad-trans_dic.xlsx
+++ b/data/trans_dic/MCS12_SP_R3-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,86; 14,93</t>
+          <t>9,01; 14,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,51; 19,34</t>
+          <t>12,88; 19,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,39; 14,54</t>
+          <t>8,06; 14,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,07; 12,99</t>
+          <t>4,69; 13,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,35; 21,93</t>
+          <t>15,25; 22,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,64; 22,46</t>
+          <t>14,63; 21,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,81; 16,55</t>
+          <t>9,71; 16,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,92; 27,94</t>
+          <t>14,75; 26,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,88; 17,45</t>
+          <t>12,88; 17,4</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,37; 19,45</t>
+          <t>14,77; 19,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,7; 14,4</t>
+          <t>9,49; 13,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,15; 18,06</t>
+          <t>10,9; 18,48</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,86; 16,06</t>
+          <t>10,86; 15,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,11; 21,57</t>
+          <t>15,09; 21,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,62; 18,79</t>
+          <t>12,43; 18,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,21; 16,09</t>
+          <t>9,16; 17,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,47; 25,21</t>
+          <t>18,41; 25,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,16; 27,22</t>
+          <t>19,76; 26,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,6; 20,85</t>
+          <t>14,71; 20,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,74; 22,32</t>
+          <t>16,66; 24,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,0; 19,34</t>
+          <t>15,04; 19,27</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,14; 22,66</t>
+          <t>18,26; 22,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14,52; 18,71</t>
+          <t>14,52; 18,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,42; 18,05</t>
+          <t>13,96; 19,42</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,88; 24,48</t>
+          <t>17,95; 24,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,9; 26,58</t>
+          <t>19,67; 26,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,05; 21,05</t>
+          <t>14,85; 20,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,02; 21,65</t>
+          <t>14,23; 20,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,75; 28,47</t>
+          <t>21,68; 28,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,64; 36,94</t>
+          <t>29,5; 37,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,52; 25,77</t>
+          <t>19,31; 25,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,18; 22,79</t>
+          <t>18,54; 23,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,94; 25,58</t>
+          <t>20,87; 25,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25,83; 30,83</t>
+          <t>25,64; 30,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,87; 22,35</t>
+          <t>18,01; 22,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,71; 21,21</t>
+          <t>17,02; 21,14</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,75; 20,38</t>
+          <t>13,84; 20,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,89; 26,18</t>
+          <t>18,91; 25,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,67; 26,32</t>
+          <t>19,48; 26,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,77; 23,56</t>
+          <t>17,92; 24,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,84; 35,35</t>
+          <t>26,76; 34,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,42; 39,3</t>
+          <t>31,63; 39,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,89; 34,03</t>
+          <t>26,94; 34,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,6; 28,46</t>
+          <t>24,09; 28,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,07; 26,83</t>
+          <t>21,3; 26,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,01; 31,53</t>
+          <t>25,94; 31,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,2; 29,34</t>
+          <t>23,9; 29,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,72; 25,01</t>
+          <t>21,78; 25,85</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,06; 30,29</t>
+          <t>21,3; 29,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,88; 32,28</t>
+          <t>22,76; 31,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,87; 25,68</t>
+          <t>17,83; 25,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20,83; 27,49</t>
+          <t>20,72; 27,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,35; 37,36</t>
+          <t>28,12; 37,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,25; 44,72</t>
+          <t>35,14; 44,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,49; 38,05</t>
+          <t>29,58; 38,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,4; 34,13</t>
+          <t>29,06; 34,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26,03; 32,18</t>
+          <t>26,19; 32,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,24; 36,86</t>
+          <t>30,3; 36,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24,94; 30,63</t>
+          <t>24,41; 30,53</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,38; 29,99</t>
+          <t>25,65; 29,88</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>28,51%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,27; 32,18</t>
+          <t>21,94; 31,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,55; 30,98</t>
+          <t>20,15; 30,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,13; 22,85</t>
+          <t>14,46; 22,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,51; 28,47</t>
+          <t>21,06; 28,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,16; 35,43</t>
+          <t>26,56; 36,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,6; 41,95</t>
+          <t>31,72; 42,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,38; 40,42</t>
+          <t>29,76; 40,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29,93; 81,11</t>
+          <t>29,25; 35,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25,77; 32,49</t>
+          <t>25,79; 32,43</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>27,83; 34,94</t>
+          <t>27,87; 35,13</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23,9; 30,58</t>
+          <t>23,76; 30,33</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>27,38; 69,66</t>
+          <t>26,3; 31,29</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20,94; 33,16</t>
+          <t>21,4; 33,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25,94; 39,02</t>
+          <t>26,2; 38,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,41; 33,98</t>
+          <t>23,57; 33,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27,34; 36,05</t>
+          <t>27,42; 36,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,62; 37,35</t>
+          <t>26,72; 37,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,97; 51,18</t>
+          <t>40,86; 51,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,7; 44,92</t>
+          <t>33,14; 44,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>39,47; 46,71</t>
+          <t>40,23; 47,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>26,1; 34,27</t>
+          <t>26,07; 33,83</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36,99; 44,85</t>
+          <t>36,81; 44,81</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30,82; 38,56</t>
+          <t>31,19; 39,11</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36,13; 41,36</t>
+          <t>36,17; 41,41</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,4; 20,22</t>
+          <t>17,28; 19,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,79; 23,79</t>
+          <t>20,95; 23,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,6; 20,27</t>
+          <t>17,61; 20,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,57; 20,4</t>
+          <t>18,1; 21,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>25,04; 28,05</t>
+          <t>25,04; 27,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,98; 34,2</t>
+          <t>31,04; 34,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,33; 28,42</t>
+          <t>25,3; 28,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>26,19; 43,77</t>
+          <t>26,5; 28,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21,74; 23,58</t>
+          <t>21,66; 23,63</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26,49; 28,69</t>
+          <t>26,52; 28,64</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21,93; 23,97</t>
+          <t>21,93; 24,0</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,81; 32,8</t>
+          <t>22,94; 24,79</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30298</t>
+          <t>36154</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>65376</t>
+          <t>73937</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95674</t>
+          <t>110091</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43772; 73744</t>
+          <t>44501; 74011</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>56832; 87842</t>
+          <t>58511; 89472</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35175; 60985</t>
+          <t>33814; 60737</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16271; 51970</t>
+          <t>19123; 55963</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>71744; 102512</t>
+          <t>71311; 104014</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62973; 96611</t>
+          <t>62950; 94396</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38823; 65513</t>
+          <t>38447; 64733</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46484; 87081</t>
+          <t>53257; 96623</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>123868; 167754</t>
+          <t>123871; 167309</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>127093; 172033</t>
+          <t>130627; 173188</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79059; 117356</t>
+          <t>77400; 113649</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>72263; 128490</t>
+          <t>83817; 142080</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49609</t>
+          <t>61097</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>90251</t>
+          <t>101337</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>139860</t>
+          <t>162434</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79909; 118084</t>
+          <t>79883; 116215</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>103811; 148205</t>
+          <t>103712; 145150</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74525; 110962</t>
+          <t>73387; 109857</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34765; 68161</t>
+          <t>43697; 81220</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>115526; 157718</t>
+          <t>115179; 156553</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>123040; 166086</t>
+          <t>120597; 164443</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82288; 117507</t>
+          <t>82882; 117771</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>54876; 114070</t>
+          <t>83368; 123898</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>204093; 263257</t>
+          <t>204675; 262309</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>235274; 294025</t>
+          <t>236910; 295903</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>167606; 215969</t>
+          <t>167528; 218298</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>106711; 168635</t>
+          <t>136485; 189797</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>96044</t>
+          <t>106728</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>108654</t>
+          <t>131121</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>204699</t>
+          <t>237848</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>114191; 156376</t>
+          <t>114615; 154739</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>135696; 181233</t>
+          <t>134115; 180230</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100704; 140866</t>
+          <t>99360; 139237</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>80424; 115933</t>
+          <t>88186; 126417</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>150003; 196346</t>
+          <t>149504; 196286</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>210703; 262556</t>
+          <t>209708; 265128</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>129088; 170436</t>
+          <t>127739; 170098</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>93090; 123484</t>
+          <t>115207; 148704</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>278186; 339823</t>
+          <t>277182; 337938</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>359763; 429394</t>
+          <t>357060; 427432</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>237824; 297314</t>
+          <t>239612; 296726</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>179987; 228427</t>
+          <t>211313; 262406</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143934</t>
+          <t>146839</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>180563</t>
+          <t>193819</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>324497</t>
+          <t>340658</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71384; 105818</t>
+          <t>71862; 106947</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>116124; 160931</t>
+          <t>116253; 158380</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>127071; 170016</t>
+          <t>125818; 171199</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>59944; 208628</t>
+          <t>125208; 170095</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>138414; 182276</t>
+          <t>137986; 179820</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>193611; 242169</t>
+          <t>194897; 244709</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>174544; 220896</t>
+          <t>174890; 221730</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>153242; 201844</t>
+          <t>176643; 212356</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>218024; 277671</t>
+          <t>220457; 274236</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>320159; 388127</t>
+          <t>319322; 388192</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>313393; 380013</t>
+          <t>309560; 378658</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>186933; 398924</t>
+          <t>311894; 370062</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>133386</t>
+          <t>143297</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>170156</t>
+          <t>192646</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>303542</t>
+          <t>335943</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>81433; 117149</t>
+          <t>82373; 115691</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>98265; 138623</t>
+          <t>97749; 136085</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>85409; 122719</t>
+          <t>85204; 122752</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>115569; 152569</t>
+          <t>124810; 163495</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>114529; 150945</t>
+          <t>113601; 151583</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>157828; 200240</t>
+          <t>157338; 200511</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>146508; 189039</t>
+          <t>146983; 189701</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>154962; 186218</t>
+          <t>176274; 210130</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>205846; 254480</t>
+          <t>207102; 255820</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>265256; 323335</t>
+          <t>265810; 323109</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>243152; 298576</t>
+          <t>237900; 297578</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>279307; 330089</t>
+          <t>310083; 361161</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>90233</t>
+          <t>98800</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>329932</t>
+          <t>140480</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>420165</t>
+          <t>239279</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>65144; 94139</t>
+          <t>64185; 93431</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>63651; 95960</t>
+          <t>62413; 94259</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47227; 76409</t>
+          <t>48341; 76199</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>78243; 103575</t>
+          <t>84668; 113045</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>89703; 121513</t>
+          <t>91089; 123558</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>111873; 148487</t>
+          <t>112303; 149370</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>114773; 152679</t>
+          <t>112415; 151572</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>181560; 492062</t>
+          <t>127885; 154788</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>163787; 206472</t>
+          <t>163882; 206067</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>184740; 231900</t>
+          <t>185027; 233218</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>170186; 217766</t>
+          <t>169208; 216008</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>265733; 676017</t>
+          <t>220747; 262622</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>88739</t>
+          <t>98096</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>181291</t>
+          <t>198480</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>270029</t>
+          <t>296576</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>43955; 69593</t>
+          <t>44907; 69622</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>64803; 97493</t>
+          <t>65455; 95600</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>60166; 87318</t>
+          <t>60570; 86511</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>76669; 101077</t>
+          <t>84339; 113183</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>88872; 124721</t>
+          <t>89216; 124835</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>159358; 199078</t>
+          <t>158933; 199999</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>134849; 179758</t>
+          <t>132626; 178728</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>164866; 195109</t>
+          <t>183354; 214465</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>141912; 186334</t>
+          <t>141783; 183957</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>236321; 286526</t>
+          <t>235167; 286242</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>202518; 253390</t>
+          <t>204942; 257028</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>252206; 288745</t>
+          <t>276146; 316121</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>632243</t>
+          <t>691011</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1126222</t>
+          <t>1031818</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1758466</t>
+          <t>1722829</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>570263; 662516</t>
+          <t>566182; 653942</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>712305; 815399</t>
+          <t>718045; 817517</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>597445; 688115</t>
+          <t>597700; 686474</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>501790; 702537</t>
+          <t>636369; 741552</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>846053; 947894</t>
+          <t>846234; 944763</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1102324; 1216963</t>
+          <t>1104449; 1223517</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>897801; 1007196</t>
+          <t>896862; 1007054</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>954129; 1594929</t>
+          <t>984640; 1076591</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1446647; 1569483</t>
+          <t>1441934; 1573020</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1850649; 2004043</t>
+          <t>1852183; 2000238</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1521629; 1663316</t>
+          <t>1521531; 1665479</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1545530; 2324808</t>
+          <t>1658876; 1792341</t>
         </is>
       </c>
     </row>
